--- a/data/trans_bre/P16A08-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P16A08-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 2,59</t>
+          <t>-2,0; 2,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 5,06</t>
+          <t>-0,42; 5,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 4,63</t>
+          <t>-1,66; 4,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 3,76</t>
+          <t>-4,69; 3,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-43,39; 112,57</t>
+          <t>-45,13; 107,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,72; 164,77</t>
+          <t>-10,69; 202,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-27,94; 169,47</t>
+          <t>-30,15; 134,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-75,47; 258,33</t>
+          <t>-75,7; 237,04</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 3,8</t>
+          <t>-0,28; 3,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 4,58</t>
+          <t>-0,16; 5,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 5,19</t>
+          <t>0,16; 4,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,04; 45,03</t>
+          <t>-0,55; 46,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 219,76</t>
+          <t>-14,95; 228,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 152,01</t>
+          <t>-6,53; 177,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,34; 202,32</t>
+          <t>-3,18; 188,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 1458,04</t>
+          <t>-11,18; 1319,27</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,19</t>
+          <t>0,58; 4,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 6,2</t>
+          <t>0,92; 6,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 6,36</t>
+          <t>1,4; 6,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 3,39</t>
+          <t>-1,16; 3,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,63; 372,35</t>
+          <t>13,5; 382,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,65; 209,37</t>
+          <t>12,3; 229,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,96; 292,3</t>
+          <t>27,74; 312,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-25,51; 143,5</t>
+          <t>-24,47; 132,21</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 3,11</t>
+          <t>-1,17; 3,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,79</t>
+          <t>1,09; 5,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,06; 5,65</t>
+          <t>1,19; 5,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 5,61</t>
+          <t>-0,02; 5,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-43,42; 297,67</t>
+          <t>-41,13; 290,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,39; 458,12</t>
+          <t>21,38; 390,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,2; 462,51</t>
+          <t>35,18; 527,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,81; 343,11</t>
+          <t>-1,41; 333,64</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 5,35</t>
+          <t>-0,16; 5,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 3,55</t>
+          <t>-0,9; 3,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 4,2</t>
+          <t>-1,33; 4,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,35</t>
+          <t>1,08; 4,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,46; 362,69</t>
+          <t>-15,83; 360,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-30,9; 344,64</t>
+          <t>-37,93; 309,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-31,68; 158,89</t>
+          <t>-27,64; 164,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>42,81; 433,89</t>
+          <t>34,77; 454,02</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,07; 5,49</t>
+          <t>0,0; 5,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 3,31</t>
+          <t>-3,49; 3,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 4,24</t>
+          <t>-0,4; 3,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 2,85</t>
+          <t>-1,67; 2,88</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-9,17; 760,69</t>
+          <t>-11,73; 903,66</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-54,91; 139,81</t>
+          <t>-54,14; 135,09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-31,03; 763,27</t>
+          <t>-29,99; 746,72</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-50,34; 215,45</t>
+          <t>-58,69; 217,02</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 2,75</t>
+          <t>-2,93; 2,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 2,76</t>
+          <t>-4,1; 2,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 3,52</t>
+          <t>-2,24; 3,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 2,19</t>
+          <t>-1,57; 2,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-79,43; 344,83</t>
+          <t>-77,61; 284,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-64,46; 151,06</t>
+          <t>-64,9; 119,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-50,09; 173,26</t>
+          <t>-53,97; 170,98</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-43,11; 178,44</t>
+          <t>-46,3; 171,59</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,4</t>
+          <t>0,64; 2,37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,07</t>
+          <t>1,09; 3,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,35</t>
+          <t>1,4; 3,27</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,78; 9,9</t>
+          <t>0,8; 10,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>21,03; 121,72</t>
+          <t>22,13; 120,77</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,38; 101,25</t>
+          <t>28,35; 108,2</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,06; 126,06</t>
+          <t>39,55; 124,15</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>21,15; 336,51</t>
+          <t>22,8; 330,72</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A08-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P16A08-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,78</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-19,38%</t>
+          <t>19,89%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 2,54</t>
+          <t>-1,95; 2,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 5,63</t>
+          <t>-0,73; 5,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 4,01</t>
+          <t>-1,43; 4,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 3,66</t>
+          <t>-2,88; 4,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-45,13; 107,13</t>
+          <t>-43,82; 119,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,69; 202,74</t>
+          <t>-14,77; 204,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-30,15; 134,04</t>
+          <t>-28,43; 172,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-75,7; 237,04</t>
+          <t>-65,25; 337,83</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13,71</t>
+          <t>1,73</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>242,48%</t>
+          <t>34,54%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 3,99</t>
+          <t>-0,52; 3,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 5,02</t>
+          <t>-0,26; 4,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 4,94</t>
+          <t>0,33; 5,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 46,17</t>
+          <t>-1,85; 5,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,95; 228,26</t>
+          <t>-19,33; 226,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 177,42</t>
+          <t>-6,84; 167,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 188,65</t>
+          <t>4,83; 208,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-11,18; 1319,27</t>
+          <t>-28,48; 146,96</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,14</t>
+          <t>1,17</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>31,17%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 4,3</t>
+          <t>0,48; 4,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 6,2</t>
+          <t>0,86; 6,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 6,39</t>
+          <t>1,66; 6,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 3,29</t>
+          <t>-1,18; 3,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,5; 382,58</t>
+          <t>12,34; 360,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,3; 229,66</t>
+          <t>14,21; 208,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,74; 312,88</t>
+          <t>36,36; 305,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-24,47; 132,21</t>
+          <t>-23,79; 127,55</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,5</t>
+          <t>1,66</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>34,64%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 3,23</t>
+          <t>-1,07; 3,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,09; 5,71</t>
+          <t>1,03; 5,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 5,78</t>
+          <t>1,38; 5,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 5,45</t>
+          <t>-0,48; 3,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-41,13; 290,38</t>
+          <t>-37,77; 272,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,38; 390,47</t>
+          <t>19,98; 412,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,18; 527,56</t>
+          <t>41,2; 461,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 333,64</t>
+          <t>-9,46; 116,04</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,73</t>
+          <t>2,58</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>167,18%</t>
+          <t>147,74%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 5,21</t>
+          <t>-0,34; 5,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 3,36</t>
+          <t>-0,87; 3,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 4,57</t>
+          <t>-1,45; 4,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,08; 4,29</t>
+          <t>0,99; 4,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,83; 360,47</t>
+          <t>-20,73; 373,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-37,93; 309,81</t>
+          <t>-36,06; 366,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-27,64; 164,47</t>
+          <t>-29,46; 168,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34,77; 454,02</t>
+          <t>30,15; 395,86</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>2,42</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>134,17%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,47</t>
+          <t>0,32; 5,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 3,1</t>
+          <t>-3,24; 3,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 3,97</t>
+          <t>-0,1; 4,41</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 2,88</t>
+          <t>0,68; 4,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-11,73; 903,66</t>
+          <t>-15,34; 755,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-54,14; 135,09</t>
+          <t>-54,41; 134,76</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-29,99; 746,72</t>
+          <t>-23,99; 725,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-58,69; 217,02</t>
+          <t>17,18; 413,58</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,49</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>27,03%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 2,59</t>
+          <t>-3,03; 2,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 2,51</t>
+          <t>-4,18; 2,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 3,42</t>
+          <t>-2,43; 3,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 2,2</t>
+          <t>-1,44; 2,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-77,61; 284,87</t>
+          <t>-78,27; 314,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-64,9; 119,41</t>
+          <t>-64,95; 114,33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-53,97; 170,98</t>
+          <t>-53,32; 188,43</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-46,3; 171,59</t>
+          <t>-41,86; 162,16</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3,02</t>
+          <t>1,57</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>46,36%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,37</t>
+          <t>0,74; 2,48</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,15</t>
+          <t>1,09; 3,09</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,27</t>
+          <t>1,37; 3,26</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,8; 10,65</t>
+          <t>0,59; 2,48</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>22,13; 120,77</t>
+          <t>25,93; 123,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,35; 108,2</t>
+          <t>27,76; 103,26</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,55; 124,15</t>
+          <t>38,82; 122,83</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>22,8; 330,72</t>
+          <t>14,09; 85,7</t>
         </is>
       </c>
     </row>
